--- a/KatalonData/Bootstrap/UM-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/UM-Data-Prod.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\Bootstrap\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t476046\Documents\VPS-Katalon-feature-VRelay\KatalonData\Bootstrap\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FBAB6183-0A86-4B81-BC4E-110F92BD5E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AFC4C0D-0621-4F60-BA6B-DC4D24F4B6D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="6" xr2:uid="{354FC140-4496-4D7F-AB69-566E59F6C646}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{354FC140-4496-4D7F-AB69-566E59F6C646}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateUser" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="88">
   <si>
     <t>Notes</t>
   </si>
@@ -148,9 +148,6 @@
     <t>Fail</t>
   </si>
   <si>
-    <t>Prod Role</t>
-  </si>
-  <si>
     <t>Tue Jun 16 23:39:10 IST 2026</t>
   </si>
   <si>
@@ -175,9 +172,6 @@
     <t>Tue Jul 07 15:58:52 EDT 2026</t>
   </si>
   <si>
-    <t>Tue Jul 07 16:02:39 EDT 2026</t>
-  </si>
-  <si>
     <t>Tue Jul 07 16:03:02 EDT 2026</t>
   </si>
   <si>
@@ -191,12 +185,133 @@
   </si>
   <si>
     <t>Tue Jul 07 16:04:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:17:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Prod Role New</t>
+  </si>
+  <si>
+    <t>Wed Sep 30 21:20:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:10:37 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:13:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:16:06 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:22:01 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:26:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:33:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Oct 08 02:47:50 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 00:14:19 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 00:16:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 00:19:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 00:25:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 00:30:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 00:36:35 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 00:51:15 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 09 21:03:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 22:30:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 22:38:03 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 22:41:11 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 22:45:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 22:48:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 22:56:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 12 23:11:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 13 19:19:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Mon Oct 19 23:57:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 00:06:36 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 00:10:32 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 00:15:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 00:18:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 00:29:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Tue Oct 20 00:36:44 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:23:28 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:24:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:24:57 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:25:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:26:30 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:27:48 IST 2026</t>
+  </si>
+  <si>
+    <t>Fri Oct 23 07:29:13 IST 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -563,25 +678,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0E041308-6561-4EE5-9DD4-5DDA2695E487}">
   <dimension ref="A1:N4"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="26.6640625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="26.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="6.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="8" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="14.1328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="9.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="26.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="23.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="29.1328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="4.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="15" max="16384" width="9.1328125" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.6640625" collapsed="true"/>
+    <col min="3" max="4" customWidth="true" style="1" width="26.6640625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="6.33203125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="14.109375" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="9.88671875" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="9.33203125" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="26.6640625" collapsed="true"/>
+    <col min="12" max="12" customWidth="true" style="1" width="23.5546875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="29.109375" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="4.88671875" collapsed="true"/>
+    <col min="15" max="16384" style="1" width="9.109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -625,18 +740,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>46</v>
+        <v>83</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -660,7 +775,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="K4" s="2"/>
     </row>
   </sheetData>
@@ -675,22 +790,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D7D96D8-F32A-42CB-8719-B4A22D28EC0D}">
   <dimension ref="A1:K2"/>
-  <sheetFormatPr defaultColWidth="19.33203125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="19.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="25.86328125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="4" width="25.86328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="6.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="8" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="8" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="13.86328125" style="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="14.6640625" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="11.33203125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="16384" width="19.33203125" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="6.5546875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="25.88671875" collapsed="true"/>
+    <col min="3" max="4" customWidth="true" style="1" width="25.88671875" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="6.33203125" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="8.0" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.88671875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="14.6640625" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="11.33203125" collapsed="true"/>
+    <col min="12" max="16384" style="1" width="19.33203125" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -725,18 +840,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>47</v>
+        <v>84</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>77</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -763,24 +878,24 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28ECF6F8-94D7-41D5-B6FF-650248E68667}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultColWidth="12.796875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.796875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="13.59765625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="4.53125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="9.33203125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="24.33203125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.44140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="24.109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="5.5546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.77734375"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="11.77734375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="8.88671875" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="8.5546875"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="8.44140625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="21.0"/>
+    <col min="12" max="13" bestFit="true" customWidth="true" width="13.5546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="4.5546875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -824,18 +939,18 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>85</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>40</v>
+      <c r="D2" t="s" s="0">
+        <v>78</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -852,10 +967,10 @@
       <c r="K2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>15</v>
       </c>
       <c r="N2" s="1" t="s">
@@ -870,100 +985,100 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5380E685-D2A4-4DCA-A76F-EFBA3980BCE7}">
   <dimension ref="A1:N2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.796875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="17.1328125" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.59765625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="13.9296875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="14" width="13.73046875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="9.33203125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="24.33203125" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="10.44140625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="24.109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="5.5546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.77734375"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="11.77734375" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.6640625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="17.109375" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="8.5546875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="8.44140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="10.5546875" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="13.88671875" collapsed="true"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="13.77734375"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" t="s" s="0">
         <v>24</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>30</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>2</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" t="s" s="0">
         <v>3</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" t="s" s="0">
         <v>12</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" t="s" s="0">
         <v>19</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" t="s" s="0">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>86</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="D2" t="s" s="0">
+        <v>79</v>
+      </c>
+      <c r="F2" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>31</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" t="s" s="0">
         <v>13</v>
       </c>
-      <c r="M2" t="s">
+      <c r="M2" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="N2">
+      <c r="N2" s="0">
         <v>13</v>
       </c>
     </row>
@@ -975,23 +1090,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6ECF5EAC-3F98-4000-BEA2-335F903FE34F}">
   <dimension ref="A1:L2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.06640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.59765625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="13.73046875" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="8.59765625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="8.44140625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="24.33203125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="7.88671875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="24.109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="5.5546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="8.77734375"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="9.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="12.6640625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="13.77734375" collapsed="true"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="8.5546875"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="8.44140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="8.88671875"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1029,18 +1144,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="28.5" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="B2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" t="s" s="0">
+        <v>87</v>
+      </c>
+      <c r="C2" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="D2" t="s">
-        <v>42</v>
+      <c r="D2" t="s" s="0">
+        <v>80</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -1069,17 +1184,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3A53983D-C89C-4548-8A02-C36CB8EC5C28}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.53125" style="3" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="4" width="29.86328125" style="3" customWidth="1" collapsed="1"/>
-    <col min="5" max="7" width="9.1328125" style="3" collapsed="1"/>
-    <col min="8" max="8" width="18.33203125" style="3" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="21" style="3" customWidth="1" collapsed="1"/>
-    <col min="10" max="16384" width="9.1328125" style="3" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="3" width="6.5546875" collapsed="true"/>
+    <col min="2" max="4" customWidth="true" style="3" width="29.88671875" collapsed="true"/>
+    <col min="5" max="7" style="3" width="9.109375" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="3" width="18.33203125" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="3" width="21.0" collapsed="true"/>
+    <col min="10" max="16384" style="3" width="9.109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1108,18 +1223,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>
@@ -1128,7 +1243,7 @@
         <v>8</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>13</v>
@@ -1142,17 +1257,17 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCABF931-E9E5-40BE-B844-C9FC3C47A38B}">
   <dimension ref="A1:I2"/>
-  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.1328125" style="3" collapsed="1"/>
-    <col min="2" max="4" width="22.6640625" style="3" customWidth="1" collapsed="1"/>
-    <col min="5" max="7" width="9.1328125" style="3" collapsed="1"/>
-    <col min="8" max="8" width="24" style="3" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="22.6640625" style="3" customWidth="1" collapsed="1"/>
-    <col min="10" max="16384" width="9.1328125" style="3" collapsed="1"/>
+    <col min="1" max="1" style="3" width="9.109375" collapsed="true"/>
+    <col min="2" max="4" customWidth="true" style="3" width="22.6640625" collapsed="true"/>
+    <col min="5" max="7" style="3" width="9.109375" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="3" width="24.0" collapsed="true"/>
+    <col min="9" max="9" customWidth="true" style="3" width="22.6640625" collapsed="true"/>
+    <col min="10" max="16384" style="3" width="9.109375" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:9" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>23</v>
       </c>
@@ -1181,18 +1296,18 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>45</v>
+        <v>82</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>

--- a/KatalonData/Bootstrap/UM-Data-Prod.xlsx
+++ b/KatalonData/Bootstrap/UM-Data-Prod.xlsx
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="98">
   <si>
     <t>Notes</t>
   </si>
@@ -305,6 +305,36 @@
   </si>
   <si>
     <t>Fri Oct 23 07:29:13 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 18:47:26 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 18:54:52 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 18:58:46 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 19:03:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 19:06:53 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 19:16:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 19:23:05 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 20:12:58 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 20:20:00 IST 2026</t>
+  </si>
+  <si>
+    <t>Wed Oct 28 20:30:40 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -751,7 +781,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -851,7 +881,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>8</v>
@@ -950,7 +980,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -1058,7 +1088,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>79</v>
+        <v>93</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>8</v>
@@ -1155,7 +1185,7 @@
         <v>14</v>
       </c>
       <c r="D2" t="s" s="0">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1" t="s">
@@ -1234,7 +1264,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>
@@ -1307,7 +1337,7 @@
         <v>14</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>8</v>
